--- a/Test/ユーザ登録 総合テスト.xlsx
+++ b/Test/ユーザ登録 総合テスト.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="109">
   <si>
     <t>テストID</t>
   </si>
@@ -125,6 +125,9 @@
     <t>1. データベースへの登録が成功すること
 2. 完了画面に遷移すること
 3. データベースに100個のデータが登録されていること</t>
+  </si>
+  <si>
+    <t>7/9 63個目まで登録完了</t>
   </si>
   <si>
     <t>UT-003</t>
@@ -862,32 +865,36 @@
         <v>20</v>
       </c>
       <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
+      <c r="J3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>31</v>
+      </c>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>18</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>20</v>
@@ -1902,13 +1909,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>12</v>
@@ -1916,181 +1923,181 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" s="2"/>
     </row>
@@ -3098,7 +3105,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -3106,16 +3113,16 @@
     </row>
     <row r="3">
       <c r="A3" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
@@ -3123,13 +3130,13 @@
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5">
@@ -3137,13 +3144,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6">
@@ -3151,13 +3158,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
@@ -3165,13 +3172,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -3179,27 +3186,27 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -3207,13 +3214,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">
@@ -3221,13 +3228,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12">
@@ -3235,13 +3242,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3249,13 +3256,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -3263,13 +3270,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15">
@@ -3277,13 +3284,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16">
@@ -3291,58 +3298,58 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1"/>

--- a/Test/ユーザ登録 総合テスト.xlsx
+++ b/Test/ユーザ登録 総合テスト.xlsx
@@ -127,7 +127,7 @@
 3. データベースに100個のデータが登録されていること</t>
   </si>
   <si>
-    <t>7/9 63個目まで登録完了</t>
+    <t>7/23 75個目まで登録完了(残り25)</t>
   </si>
   <si>
     <t>UT-003</t>

--- a/Test/ユーザ登録 総合テスト.xlsx
+++ b/Test/ユーザ登録 総合テスト.xlsx
@@ -15,58 +15,173 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="109">
   <si>
+    <t>観点カテゴリ</t>
+  </si>
+  <si>
+    <t>単体テスト仕様書テンプレート 使い方ガイド</t>
+  </si>
+  <si>
     <t>テストID</t>
   </si>
   <si>
+    <t>チェック項目</t>
+  </si>
+  <si>
+    <t>確認済</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>入力値検証</t>
+  </si>
+  <si>
     <t>機能名</t>
   </si>
   <si>
+    <t>正常値（代表値）のテストケースを作成したか</t>
+  </si>
+  <si>
     <t>テスト観点・目的</t>
   </si>
   <si>
+    <t>□</t>
+  </si>
+  <si>
+    <t>項目名</t>
+  </si>
+  <si>
     <t>前提条件</t>
   </si>
   <si>
     <t>テスト手順</t>
   </si>
   <si>
+    <t>境界値（最小値・最大値）のテストケースを作成したか</t>
+  </si>
+  <si>
+    <t>説明</t>
+  </si>
+  <si>
     <t>テストデータ（入力値）</t>
   </si>
   <si>
+    <t>記載例</t>
+  </si>
+  <si>
     <t>期待結果</t>
   </si>
   <si>
+    <t>注意点</t>
+  </si>
+  <si>
     <t>優先度</t>
   </si>
   <si>
+    <t>空文字・Nullのテストケースを作成したか</t>
+  </si>
+  <si>
     <t>実施日</t>
   </si>
   <si>
+    <t>各テストケースを一意に識別するID</t>
+  </si>
+  <si>
+    <t>UT-001, UT-002</t>
+  </si>
+  <si>
     <t>実施者</t>
   </si>
   <si>
+    <t>プロジェクト内で重複しないように採番</t>
+  </si>
+  <si>
+    <t>不正な形式・特殊文字のテストケースを作成したか</t>
+  </si>
+  <si>
     <t>実測結果</t>
   </si>
   <si>
     <t>合否判定</t>
   </si>
   <si>
-    <t>備考</t>
+    <t>テスト対象の機能やクラス名</t>
+  </si>
+  <si>
+    <t>ログイン認証、ユーザー登録</t>
+  </si>
+  <si>
+    <t>機能動作</t>
+  </si>
+  <si>
+    <t>要件定義書・設計書と用語を統一</t>
+  </si>
+  <si>
+    <t>正常系の動作確認ケースを作成したか</t>
   </si>
   <si>
     <t>UT-001</t>
   </si>
   <si>
+    <t>何を確認するテストか</t>
+  </si>
+  <si>
     <t>データベースへの保存</t>
   </si>
   <si>
+    <t>入力値チェック、正常系動作確認</t>
+  </si>
+  <si>
+    <t>具体的な検証ポイントを明記</t>
+  </si>
+  <si>
+    <t>異常系のエラー処理ケースを作成したか</t>
+  </si>
+  <si>
+    <t>テスト実行前に整える条件</t>
+  </si>
+  <si>
+    <t>ログイン画面が表示されている状態</t>
+  </si>
+  <si>
+    <t>環境設定、データ状態なども記載</t>
+  </si>
+  <si>
+    <t>具体的な実行ステップ</t>
+  </si>
+  <si>
+    <t>1. ユーザーID欄に入力
+2. ボタンをクリック</t>
+  </si>
+  <si>
+    <t>番号付きで誰でも実行できるよう詳細に</t>
+  </si>
+  <si>
     <t>保存値が正常か</t>
   </si>
   <si>
+    <t>例外処理の確認ケースを作成したか</t>
+  </si>
+  <si>
+    <t>テストデータ</t>
+  </si>
+  <si>
     <t>確認画面が表示されている状態</t>
   </si>
   <si>
+    <t>使用する入力値の詳細</t>
+  </si>
+  <si>
     <t>１．確認画面に表示された「登録する」ボタンを押す。</t>
+  </si>
+  <si>
+    <t>ユーザーID=test001</t>
+  </si>
+  <si>
+    <t>画面表示</t>
+  </si>
+  <si>
+    <t>正常値、境界値、異常値を網羅</t>
   </si>
   <si>
     <t>"名前（姓）=ひらがな・漢字・10文字以内
@@ -84,33 +199,93 @@
 （※登録画面にて入力する内容）"</t>
   </si>
   <si>
+    <t>期待する画面遷移のケースを作成したか</t>
+  </si>
+  <si>
     <t>完了画面に遷移し、データベースの各々の欄に入力・選択した内容が表示されている。
 (パスワードに関してはハッシュ化されたものが表示されている。)</t>
   </si>
   <si>
+    <t>成功時に得られるべき出力</t>
+  </si>
+  <si>
     <t>高</t>
   </si>
   <si>
+    <t>エラーメッセージ「〇〇」が表示</t>
+  </si>
+  <si>
+    <t>曖昧な表現を避け具体的に記載</t>
+  </si>
+  <si>
+    <t>エラーメッセージ表示のケースを作成したか</t>
+  </si>
+  <si>
+    <t>テストの重要度</t>
+  </si>
+  <si>
+    <t>高・中・低</t>
+  </si>
+  <si>
+    <t>リスクや影響度に応じて設定</t>
+  </si>
+  <si>
+    <t>必須項目のバリデーションケースを作成したか</t>
+  </si>
+  <si>
+    <t>テスト実行日</t>
+  </si>
+  <si>
     <t>山本穂乃花</t>
   </si>
   <si>
+    <t>2025/10/15</t>
+  </si>
+  <si>
+    <t>データ処理</t>
+  </si>
+  <si>
+    <t>実行後に記入</t>
+  </si>
+  <si>
+    <t>データベース登録・更新のケースを作成したか</t>
+  </si>
+  <si>
     <t>郵便番号の最初を「00」にした所、登録されず5桁だけ登録されてしまった</t>
   </si>
   <si>
     <t>否</t>
+  </si>
+  <si>
+    <t>テスト実行者名</t>
   </si>
   <si>
     <t>確認画面ではきちんと表示されていた。実際に0から始まる郵便番号はある為正常に登録する為にもデータベースの値を変更する必要がある。
 （現在の郵便番号の値→int）</t>
   </si>
   <si>
+    <t>山田太郎</t>
+  </si>
+  <si>
+    <t>データベース削除のケースを作成したか</t>
+  </si>
+  <si>
     <t>UT-002</t>
   </si>
   <si>
     <t>負荷テスト</t>
   </si>
   <si>
+    <t>実際の出力結果</t>
+  </si>
+  <si>
+    <t>エラーメッセージが表示された</t>
+  </si>
+  <si>
     <t>想定している数まで登録可能か</t>
+  </si>
+  <si>
+    <t>データ検索・取得のケースを作成したか</t>
   </si>
   <si>
     <t>ユーザー登録画面が表示されている状態</t>
@@ -122,21 +297,45 @@
 上記内容をデータベースのデータが100個になるまで繰り返す</t>
   </si>
   <si>
+    <t>権限・認証</t>
+  </si>
+  <si>
+    <t>権限チェックのケースを作成したか</t>
+  </si>
+  <si>
+    <t>期待結果との比較結果</t>
+  </si>
+  <si>
     <t>1. データベースへの登録が成功すること
 2. 完了画面に遷移すること
 3. データベースに100個のデータが登録されていること</t>
   </si>
   <si>
-    <t>7/23 75個目まで登録完了(残り25)</t>
+    <t>○（合格）、×（不合格）</t>
+  </si>
+  <si>
+    <t>ログイン状態の確認ケースを作成したか</t>
+  </si>
+  <si>
+    <t>7/29 82個目まで登録完了(残り18)</t>
+  </si>
+  <si>
+    <t>その他特記事項</t>
+  </si>
+  <si>
+    <t>不具合管理番号:BUG-123</t>
   </si>
   <si>
     <t>UT-003</t>
   </si>
   <si>
+    <t>必要に応じて追加情報を記載</t>
+  </si>
+  <si>
+    <t>【重要なポイント】</t>
+  </si>
+  <si>
     <t>過剰登録したらエラーが出るか</t>
-  </si>
-  <si>
-    <t>ログイン画面が表示されている状態</t>
   </si>
   <si>
     <t>1. データベースに100個のデータを登録する
@@ -144,212 +343,13 @@
 3．確認画面に移行し、「登録する」ボタンを押す</t>
   </si>
   <si>
+    <t>✓</t>
+  </si>
+  <si>
+    <t>期待結果は具体的に記載し、曖昧な表現を避ける</t>
+  </si>
+  <si>
     <t>完了画面に遷移せず、エラーが表示される</t>
-  </si>
-  <si>
-    <t>観点カテゴリ</t>
-  </si>
-  <si>
-    <t>チェック項目</t>
-  </si>
-  <si>
-    <t>確認済</t>
-  </si>
-  <si>
-    <t>入力値検証</t>
-  </si>
-  <si>
-    <t>正常値（代表値）のテストケースを作成したか</t>
-  </si>
-  <si>
-    <t>□</t>
-  </si>
-  <si>
-    <t>境界値（最小値・最大値）のテストケースを作成したか</t>
-  </si>
-  <si>
-    <t>空文字・Nullのテストケースを作成したか</t>
-  </si>
-  <si>
-    <t>不正な形式・特殊文字のテストケースを作成したか</t>
-  </si>
-  <si>
-    <t>機能動作</t>
-  </si>
-  <si>
-    <t>正常系の動作確認ケースを作成したか</t>
-  </si>
-  <si>
-    <t>異常系のエラー処理ケースを作成したか</t>
-  </si>
-  <si>
-    <t>例外処理の確認ケースを作成したか</t>
-  </si>
-  <si>
-    <t>画面表示</t>
-  </si>
-  <si>
-    <t>期待する画面遷移のケースを作成したか</t>
-  </si>
-  <si>
-    <t>エラーメッセージ表示のケースを作成したか</t>
-  </si>
-  <si>
-    <t>必須項目のバリデーションケースを作成したか</t>
-  </si>
-  <si>
-    <t>データ処理</t>
-  </si>
-  <si>
-    <t>データベース登録・更新のケースを作成したか</t>
-  </si>
-  <si>
-    <t>データベース削除のケースを作成したか</t>
-  </si>
-  <si>
-    <t>データ検索・取得のケースを作成したか</t>
-  </si>
-  <si>
-    <t>権限・認証</t>
-  </si>
-  <si>
-    <t>権限チェックのケースを作成したか</t>
-  </si>
-  <si>
-    <t>ログイン状態の確認ケースを作成したか</t>
-  </si>
-  <si>
-    <t>単体テスト仕様書テンプレート 使い方ガイド</t>
-  </si>
-  <si>
-    <t>項目名</t>
-  </si>
-  <si>
-    <t>説明</t>
-  </si>
-  <si>
-    <t>記載例</t>
-  </si>
-  <si>
-    <t>注意点</t>
-  </si>
-  <si>
-    <t>各テストケースを一意に識別するID</t>
-  </si>
-  <si>
-    <t>UT-001, UT-002</t>
-  </si>
-  <si>
-    <t>プロジェクト内で重複しないように採番</t>
-  </si>
-  <si>
-    <t>テスト対象の機能やクラス名</t>
-  </si>
-  <si>
-    <t>ログイン認証、ユーザー登録</t>
-  </si>
-  <si>
-    <t>要件定義書・設計書と用語を統一</t>
-  </si>
-  <si>
-    <t>何を確認するテストか</t>
-  </si>
-  <si>
-    <t>入力値チェック、正常系動作確認</t>
-  </si>
-  <si>
-    <t>具体的な検証ポイントを明記</t>
-  </si>
-  <si>
-    <t>テスト実行前に整える条件</t>
-  </si>
-  <si>
-    <t>環境設定、データ状態なども記載</t>
-  </si>
-  <si>
-    <t>具体的な実行ステップ</t>
-  </si>
-  <si>
-    <t>1. ユーザーID欄に入力
-2. ボタンをクリック</t>
-  </si>
-  <si>
-    <t>番号付きで誰でも実行できるよう詳細に</t>
-  </si>
-  <si>
-    <t>テストデータ</t>
-  </si>
-  <si>
-    <t>使用する入力値の詳細</t>
-  </si>
-  <si>
-    <t>ユーザーID=test001</t>
-  </si>
-  <si>
-    <t>正常値、境界値、異常値を網羅</t>
-  </si>
-  <si>
-    <t>成功時に得られるべき出力</t>
-  </si>
-  <si>
-    <t>エラーメッセージ「〇〇」が表示</t>
-  </si>
-  <si>
-    <t>曖昧な表現を避け具体的に記載</t>
-  </si>
-  <si>
-    <t>テストの重要度</t>
-  </si>
-  <si>
-    <t>高・中・低</t>
-  </si>
-  <si>
-    <t>リスクや影響度に応じて設定</t>
-  </si>
-  <si>
-    <t>テスト実行日</t>
-  </si>
-  <si>
-    <t>2025/10/15</t>
-  </si>
-  <si>
-    <t>実行後に記入</t>
-  </si>
-  <si>
-    <t>テスト実行者名</t>
-  </si>
-  <si>
-    <t>山田太郎</t>
-  </si>
-  <si>
-    <t>実際の出力結果</t>
-  </si>
-  <si>
-    <t>エラーメッセージが表示された</t>
-  </si>
-  <si>
-    <t>期待結果との比較結果</t>
-  </si>
-  <si>
-    <t>○（合格）、×（不合格）</t>
-  </si>
-  <si>
-    <t>その他特記事項</t>
-  </si>
-  <si>
-    <t>不具合管理番号:BUG-123</t>
-  </si>
-  <si>
-    <t>必要に応じて追加情報を記載</t>
-  </si>
-  <si>
-    <t>【重要なポイント】</t>
-  </si>
-  <si>
-    <t>✓</t>
-  </si>
-  <si>
-    <t>期待結果は具体的に記載し、曖昧な表現を避ける</t>
   </si>
   <si>
     <t>テスト手順は番号を付けて、誰でも実行できるよう詳細に記載</t>
@@ -386,11 +386,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <b/>
       <sz val="14.0"/>
       <color rgb="FFFFFFFF"/>
@@ -398,6 +393,11 @@
       <scheme val="minor"/>
     </font>
     <font/>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <b/>
       <sz val="11.0"/>
@@ -491,28 +491,28 @@
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
@@ -759,151 +759,151 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="4">
+      <c r="A2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" s="8">
         <v>46208.0</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>24</v>
+      <c r="J2" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
+      <c r="A3" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
+      <c r="A4" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -1909,197 +1909,197 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="2"/>
+      <c r="A2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="2"/>
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="2"/>
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="2"/>
+      <c r="A5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="4"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="2"/>
+      <c r="A6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="4"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="2"/>
+      <c r="A7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="4"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="2"/>
+      <c r="A8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="4"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="2"/>
+      <c r="A9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="4"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="2"/>
+      <c r="A10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="4"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="2"/>
+      <c r="A11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="4"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="2"/>
+      <c r="A12" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="4"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="2"/>
+      <c r="A13" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="4"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="2"/>
+      <c r="A14" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="4"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="2"/>
+      <c r="A15" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="4"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="2"/>
+      <c r="A16" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="4"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -3104,225 +3104,225 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="9"/>
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>65</v>
+      <c r="A3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>68</v>
+      <c r="A4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>71</v>
+      <c r="A5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>74</v>
+      <c r="A6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>76</v>
+      <c r="A7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>79</v>
+      <c r="A8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>83</v>
+      <c r="A9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>86</v>
+      <c r="A10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>89</v>
+      <c r="A11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>92</v>
+      <c r="A12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>92</v>
+      <c r="A13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>92</v>
+      <c r="A14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="A15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>92</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>101</v>
+      <c r="A16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>103</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>105</v>
@@ -3330,7 +3330,7 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>106</v>
@@ -3338,7 +3338,7 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>107</v>
@@ -3346,7 +3346,7 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>108</v>

--- a/Test/ユーザ登録 総合テスト.xlsx
+++ b/Test/ユーザ登録 総合テスト.xlsx
@@ -15,173 +15,58 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="109">
   <si>
-    <t>観点カテゴリ</t>
-  </si>
-  <si>
-    <t>単体テスト仕様書テンプレート 使い方ガイド</t>
-  </si>
-  <si>
     <t>テストID</t>
   </si>
   <si>
-    <t>チェック項目</t>
-  </si>
-  <si>
-    <t>確認済</t>
+    <t>機能名</t>
+  </si>
+  <si>
+    <t>テスト観点・目的</t>
+  </si>
+  <si>
+    <t>前提条件</t>
+  </si>
+  <si>
+    <t>テスト手順</t>
+  </si>
+  <si>
+    <t>テストデータ（入力値）</t>
+  </si>
+  <si>
+    <t>期待結果</t>
+  </si>
+  <si>
+    <t>優先度</t>
+  </si>
+  <si>
+    <t>実施日</t>
+  </si>
+  <si>
+    <t>実施者</t>
+  </si>
+  <si>
+    <t>実測結果</t>
+  </si>
+  <si>
+    <t>合否判定</t>
   </si>
   <si>
     <t>備考</t>
   </si>
   <si>
-    <t>入力値検証</t>
-  </si>
-  <si>
-    <t>機能名</t>
-  </si>
-  <si>
-    <t>正常値（代表値）のテストケースを作成したか</t>
-  </si>
-  <si>
-    <t>テスト観点・目的</t>
-  </si>
-  <si>
-    <t>□</t>
-  </si>
-  <si>
-    <t>項目名</t>
-  </si>
-  <si>
-    <t>前提条件</t>
-  </si>
-  <si>
-    <t>テスト手順</t>
-  </si>
-  <si>
-    <t>境界値（最小値・最大値）のテストケースを作成したか</t>
-  </si>
-  <si>
-    <t>説明</t>
-  </si>
-  <si>
-    <t>テストデータ（入力値）</t>
-  </si>
-  <si>
-    <t>記載例</t>
-  </si>
-  <si>
-    <t>期待結果</t>
-  </si>
-  <si>
-    <t>注意点</t>
-  </si>
-  <si>
-    <t>優先度</t>
-  </si>
-  <si>
-    <t>空文字・Nullのテストケースを作成したか</t>
-  </si>
-  <si>
-    <t>実施日</t>
-  </si>
-  <si>
-    <t>各テストケースを一意に識別するID</t>
-  </si>
-  <si>
-    <t>UT-001, UT-002</t>
-  </si>
-  <si>
-    <t>実施者</t>
-  </si>
-  <si>
-    <t>プロジェクト内で重複しないように採番</t>
-  </si>
-  <si>
-    <t>不正な形式・特殊文字のテストケースを作成したか</t>
-  </si>
-  <si>
-    <t>実測結果</t>
-  </si>
-  <si>
-    <t>合否判定</t>
-  </si>
-  <si>
-    <t>テスト対象の機能やクラス名</t>
-  </si>
-  <si>
-    <t>ログイン認証、ユーザー登録</t>
-  </si>
-  <si>
-    <t>機能動作</t>
-  </si>
-  <si>
-    <t>要件定義書・設計書と用語を統一</t>
-  </si>
-  <si>
-    <t>正常系の動作確認ケースを作成したか</t>
-  </si>
-  <si>
     <t>UT-001</t>
   </si>
   <si>
-    <t>何を確認するテストか</t>
-  </si>
-  <si>
     <t>データベースへの保存</t>
   </si>
   <si>
-    <t>入力値チェック、正常系動作確認</t>
-  </si>
-  <si>
-    <t>具体的な検証ポイントを明記</t>
-  </si>
-  <si>
-    <t>異常系のエラー処理ケースを作成したか</t>
-  </si>
-  <si>
-    <t>テスト実行前に整える条件</t>
-  </si>
-  <si>
-    <t>ログイン画面が表示されている状態</t>
-  </si>
-  <si>
-    <t>環境設定、データ状態なども記載</t>
-  </si>
-  <si>
-    <t>具体的な実行ステップ</t>
-  </si>
-  <si>
-    <t>1. ユーザーID欄に入力
-2. ボタンをクリック</t>
-  </si>
-  <si>
-    <t>番号付きで誰でも実行できるよう詳細に</t>
-  </si>
-  <si>
     <t>保存値が正常か</t>
   </si>
   <si>
-    <t>例外処理の確認ケースを作成したか</t>
-  </si>
-  <si>
-    <t>テストデータ</t>
-  </si>
-  <si>
     <t>確認画面が表示されている状態</t>
   </si>
   <si>
-    <t>使用する入力値の詳細</t>
-  </si>
-  <si>
     <t>１．確認画面に表示された「登録する」ボタンを押す。</t>
-  </si>
-  <si>
-    <t>ユーザーID=test001</t>
-  </si>
-  <si>
-    <t>画面表示</t>
-  </si>
-  <si>
-    <t>正常値、境界値、異常値を網羅</t>
   </si>
   <si>
     <t>"名前（姓）=ひらがな・漢字・10文字以内
@@ -199,93 +84,42 @@
 （※登録画面にて入力する内容）"</t>
   </si>
   <si>
-    <t>期待する画面遷移のケースを作成したか</t>
-  </si>
-  <si>
     <t>完了画面に遷移し、データベースの各々の欄に入力・選択した内容が表示されている。
 (パスワードに関してはハッシュ化されたものが表示されている。)</t>
   </si>
   <si>
-    <t>成功時に得られるべき出力</t>
-  </si>
-  <si>
     <t>高</t>
   </si>
   <si>
-    <t>エラーメッセージ「〇〇」が表示</t>
-  </si>
-  <si>
-    <t>曖昧な表現を避け具体的に記載</t>
-  </si>
-  <si>
-    <t>エラーメッセージ表示のケースを作成したか</t>
-  </si>
-  <si>
-    <t>テストの重要度</t>
-  </si>
-  <si>
-    <t>高・中・低</t>
-  </si>
-  <si>
-    <t>リスクや影響度に応じて設定</t>
-  </si>
-  <si>
-    <t>必須項目のバリデーションケースを作成したか</t>
-  </si>
-  <si>
-    <t>テスト実行日</t>
-  </si>
-  <si>
     <t>山本穂乃花</t>
   </si>
   <si>
-    <t>2025/10/15</t>
-  </si>
-  <si>
-    <t>データ処理</t>
-  </si>
-  <si>
-    <t>実行後に記入</t>
-  </si>
-  <si>
-    <t>データベース登録・更新のケースを作成したか</t>
-  </si>
-  <si>
     <t>郵便番号の最初を「00」にした所、登録されず5桁だけ登録されてしまった</t>
   </si>
   <si>
+    <t>観点カテゴリ</t>
+  </si>
+  <si>
     <t>否</t>
-  </si>
-  <si>
-    <t>テスト実行者名</t>
   </si>
   <si>
     <t>確認画面ではきちんと表示されていた。実際に0から始まる郵便番号はある為正常に登録する為にもデータベースの値を変更する必要がある。
 （現在の郵便番号の値→int）</t>
   </si>
   <si>
-    <t>山田太郎</t>
-  </si>
-  <si>
-    <t>データベース削除のケースを作成したか</t>
-  </si>
-  <si>
     <t>UT-002</t>
   </si>
   <si>
+    <t>チェック項目</t>
+  </si>
+  <si>
     <t>負荷テスト</t>
   </si>
   <si>
-    <t>実際の出力結果</t>
-  </si>
-  <si>
-    <t>エラーメッセージが表示された</t>
+    <t>確認済</t>
   </si>
   <si>
     <t>想定している数まで登録可能か</t>
-  </si>
-  <si>
-    <t>データ検索・取得のケースを作成したか</t>
   </si>
   <si>
     <t>ユーザー登録画面が表示されている状態</t>
@@ -297,13 +131,10 @@
 上記内容をデータベースのデータが100個になるまで繰り返す</t>
   </si>
   <si>
-    <t>権限・認証</t>
-  </si>
-  <si>
-    <t>権限チェックのケースを作成したか</t>
-  </si>
-  <si>
-    <t>期待結果との比較結果</t>
+    <t>入力値検証</t>
+  </si>
+  <si>
+    <t>正常値（代表値）のテストケースを作成したか</t>
   </si>
   <si>
     <t>1. データベースへの登録が成功すること
@@ -311,31 +142,25 @@
 3. データベースに100個のデータが登録されていること</t>
   </si>
   <si>
-    <t>○（合格）、×（不合格）</t>
-  </si>
-  <si>
-    <t>ログイン状態の確認ケースを作成したか</t>
-  </si>
-  <si>
-    <t>7/29 82個目まで登録完了(残り18)</t>
-  </si>
-  <si>
-    <t>その他特記事項</t>
-  </si>
-  <si>
-    <t>不具合管理番号:BUG-123</t>
+    <t>□</t>
+  </si>
+  <si>
+    <t>境界値（最小値・最大値）のテストケースを作成したか</t>
+  </si>
+  <si>
+    <t>8/13 92個目まで登録完了(残り8)</t>
   </si>
   <si>
     <t>UT-003</t>
   </si>
   <si>
-    <t>必要に応じて追加情報を記載</t>
-  </si>
-  <si>
-    <t>【重要なポイント】</t>
+    <t>空文字・Nullのテストケースを作成したか</t>
   </si>
   <si>
     <t>過剰登録したらエラーが出るか</t>
+  </si>
+  <si>
+    <t>ログイン画面が表示されている状態</t>
   </si>
   <si>
     <t>1. データベースに100個のデータを登録する
@@ -343,13 +168,188 @@
 3．確認画面に移行し、「登録する」ボタンを押す</t>
   </si>
   <si>
+    <t>不正な形式・特殊文字のテストケースを作成したか</t>
+  </si>
+  <si>
+    <t>完了画面に遷移せず、エラーが表示される</t>
+  </si>
+  <si>
+    <t>機能動作</t>
+  </si>
+  <si>
+    <t>正常系の動作確認ケースを作成したか</t>
+  </si>
+  <si>
+    <t>異常系のエラー処理ケースを作成したか</t>
+  </si>
+  <si>
+    <t>例外処理の確認ケースを作成したか</t>
+  </si>
+  <si>
+    <t>画面表示</t>
+  </si>
+  <si>
+    <t>期待する画面遷移のケースを作成したか</t>
+  </si>
+  <si>
+    <t>エラーメッセージ表示のケースを作成したか</t>
+  </si>
+  <si>
+    <t>必須項目のバリデーションケースを作成したか</t>
+  </si>
+  <si>
+    <t>データ処理</t>
+  </si>
+  <si>
+    <t>データベース登録・更新のケースを作成したか</t>
+  </si>
+  <si>
+    <t>データベース削除のケースを作成したか</t>
+  </si>
+  <si>
+    <t>データ検索・取得のケースを作成したか</t>
+  </si>
+  <si>
+    <t>権限・認証</t>
+  </si>
+  <si>
+    <t>権限チェックのケースを作成したか</t>
+  </si>
+  <si>
+    <t>ログイン状態の確認ケースを作成したか</t>
+  </si>
+  <si>
+    <t>単体テスト仕様書テンプレート 使い方ガイド</t>
+  </si>
+  <si>
+    <t>項目名</t>
+  </si>
+  <si>
+    <t>説明</t>
+  </si>
+  <si>
+    <t>記載例</t>
+  </si>
+  <si>
+    <t>注意点</t>
+  </si>
+  <si>
+    <t>各テストケースを一意に識別するID</t>
+  </si>
+  <si>
+    <t>UT-001, UT-002</t>
+  </si>
+  <si>
+    <t>プロジェクト内で重複しないように採番</t>
+  </si>
+  <si>
+    <t>テスト対象の機能やクラス名</t>
+  </si>
+  <si>
+    <t>ログイン認証、ユーザー登録</t>
+  </si>
+  <si>
+    <t>要件定義書・設計書と用語を統一</t>
+  </si>
+  <si>
+    <t>何を確認するテストか</t>
+  </si>
+  <si>
+    <t>入力値チェック、正常系動作確認</t>
+  </si>
+  <si>
+    <t>具体的な検証ポイントを明記</t>
+  </si>
+  <si>
+    <t>テスト実行前に整える条件</t>
+  </si>
+  <si>
+    <t>環境設定、データ状態なども記載</t>
+  </si>
+  <si>
+    <t>具体的な実行ステップ</t>
+  </si>
+  <si>
+    <t>1. ユーザーID欄に入力
+2. ボタンをクリック</t>
+  </si>
+  <si>
+    <t>番号付きで誰でも実行できるよう詳細に</t>
+  </si>
+  <si>
+    <t>テストデータ</t>
+  </si>
+  <si>
+    <t>使用する入力値の詳細</t>
+  </si>
+  <si>
+    <t>ユーザーID=test001</t>
+  </si>
+  <si>
+    <t>正常値、境界値、異常値を網羅</t>
+  </si>
+  <si>
+    <t>成功時に得られるべき出力</t>
+  </si>
+  <si>
+    <t>エラーメッセージ「〇〇」が表示</t>
+  </si>
+  <si>
+    <t>曖昧な表現を避け具体的に記載</t>
+  </si>
+  <si>
+    <t>テストの重要度</t>
+  </si>
+  <si>
+    <t>高・中・低</t>
+  </si>
+  <si>
+    <t>リスクや影響度に応じて設定</t>
+  </si>
+  <si>
+    <t>テスト実行日</t>
+  </si>
+  <si>
+    <t>2025/10/15</t>
+  </si>
+  <si>
+    <t>実行後に記入</t>
+  </si>
+  <si>
+    <t>テスト実行者名</t>
+  </si>
+  <si>
+    <t>山田太郎</t>
+  </si>
+  <si>
+    <t>実際の出力結果</t>
+  </si>
+  <si>
+    <t>エラーメッセージが表示された</t>
+  </si>
+  <si>
+    <t>期待結果との比較結果</t>
+  </si>
+  <si>
+    <t>○（合格）、×（不合格）</t>
+  </si>
+  <si>
+    <t>その他特記事項</t>
+  </si>
+  <si>
+    <t>不具合管理番号:BUG-123</t>
+  </si>
+  <si>
+    <t>必要に応じて追加情報を記載</t>
+  </si>
+  <si>
+    <t>【重要なポイント】</t>
+  </si>
+  <si>
     <t>✓</t>
   </si>
   <si>
     <t>期待結果は具体的に記載し、曖昧な表現を避ける</t>
-  </si>
-  <si>
-    <t>完了画面に遷移せず、エラーが表示される</t>
   </si>
   <si>
     <t>テスト手順は番号を付けて、誰でも実行できるよう詳細に記載</t>
@@ -386,6 +386,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <sz val="14.0"/>
       <color rgb="FFFFFFFF"/>
@@ -393,11 +398,6 @@
       <scheme val="minor"/>
     </font>
     <font/>
-    <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
     <font>
       <b/>
       <sz val="11.0"/>
@@ -491,28 +491,28 @@
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
@@ -759,151 +759,151 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="I2" s="8">
+      <c r="A2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="4">
         <v>46208.0</v>
       </c>
-      <c r="J2" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>77</v>
+      <c r="J2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
+      <c r="A3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="A4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
+      <c r="E4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -1909,197 +1909,197 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="4"/>
+      <c r="A2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="4"/>
+      <c r="A3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="2"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="4"/>
+      <c r="A4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="4"/>
+      <c r="A5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="2"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="4"/>
+      <c r="A6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="2"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="4"/>
+      <c r="A7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="4"/>
+      <c r="A8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="2"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="4"/>
+      <c r="A9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="2"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="4"/>
+      <c r="A10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="2"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="4"/>
+      <c r="A11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="2"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="4"/>
+      <c r="A12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="2"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="4"/>
+      <c r="A13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="2"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="4"/>
+      <c r="A14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="2"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="4"/>
+      <c r="A15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="2"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="4"/>
+      <c r="A16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="2"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -3104,225 +3104,225 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="5"/>
+      <c r="A1" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="9"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>19</v>
+      <c r="A3" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>26</v>
+      <c r="A4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>33</v>
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>39</v>
+      <c r="A6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="A7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>43</v>
+      <c r="D7" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>46</v>
+      <c r="A8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>55</v>
+      <c r="A9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>62</v>
+      <c r="A10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>66</v>
+      <c r="A11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>72</v>
+      <c r="A12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>72</v>
+      <c r="A13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>72</v>
+      <c r="A14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="A15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>98</v>
+      <c r="A16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>105</v>
@@ -3330,7 +3330,7 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>106</v>
@@ -3338,7 +3338,7 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>107</v>
@@ -3346,7 +3346,7 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>108</v>

--- a/Test/ユーザ登録 総合テスト.xlsx
+++ b/Test/ユーザ登録 総合テスト.xlsx
@@ -13,11 +13,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="111">
   <si>
     <t>テストID</t>
   </si>
   <si>
+    <t>観点カテゴリ</t>
+  </si>
+  <si>
+    <t>単体テスト仕様書テンプレート 使い方ガイド</t>
+  </si>
+  <si>
     <t>機能名</t>
   </si>
   <si>
@@ -27,6 +33,9 @@
     <t>前提条件</t>
   </si>
   <si>
+    <t>チェック項目</t>
+  </si>
+  <si>
     <t>テスト手順</t>
   </si>
   <si>
@@ -36,12 +45,18 @@
     <t>期待結果</t>
   </si>
   <si>
+    <t>確認済</t>
+  </si>
+  <si>
     <t>優先度</t>
   </si>
   <si>
     <t>実施日</t>
   </si>
   <si>
+    <t>備考</t>
+  </si>
+  <si>
     <t>実施者</t>
   </si>
   <si>
@@ -51,13 +66,22 @@
     <t>合否判定</t>
   </si>
   <si>
-    <t>備考</t>
+    <t>入力値検証</t>
   </si>
   <si>
     <t>UT-001</t>
   </si>
   <si>
+    <t>正常値（代表値）のテストケースを作成したか</t>
+  </si>
+  <si>
     <t>データベースへの保存</t>
+  </si>
+  <si>
+    <t>□</t>
+  </si>
+  <si>
+    <t>境界値（最小値・最大値）のテストケースを作成したか</t>
   </si>
   <si>
     <t>保存値が正常か</t>
@@ -84,6 +108,9 @@
 （※登録画面にて入力する内容）"</t>
   </si>
   <si>
+    <t>空文字・Nullのテストケースを作成したか</t>
+  </si>
+  <si>
     <t>完了画面に遷移し、データベースの各々の欄に入力・選択した内容が表示されている。
 (パスワードに関してはハッシュ化されたものが表示されている。)</t>
   </si>
@@ -91,13 +118,34 @@
     <t>高</t>
   </si>
   <si>
+    <t>項目名</t>
+  </si>
+  <si>
+    <t>不正な形式・特殊文字のテストケースを作成したか</t>
+  </si>
+  <si>
+    <t>説明</t>
+  </si>
+  <si>
+    <t>機能動作</t>
+  </si>
+  <si>
+    <t>記載例</t>
+  </si>
+  <si>
+    <t>正常系の動作確認ケースを作成したか</t>
+  </si>
+  <si>
+    <t>注意点</t>
+  </si>
+  <si>
     <t>山本穂乃花</t>
   </si>
   <si>
     <t>郵便番号の最初を「00」にした所、登録されず5桁だけ登録されてしまった</t>
   </si>
   <si>
-    <t>観点カテゴリ</t>
+    <t>異常系のエラー処理ケースを作成したか</t>
   </si>
   <si>
     <t>否</t>
@@ -107,22 +155,34 @@
 （現在の郵便番号の値→int）</t>
   </si>
   <si>
+    <t>各テストケースを一意に識別するID</t>
+  </si>
+  <si>
     <t>UT-002</t>
   </si>
   <si>
-    <t>チェック項目</t>
+    <t>UT-001, UT-002</t>
+  </si>
+  <si>
+    <t>例外処理の確認ケースを作成したか</t>
   </si>
   <si>
     <t>負荷テスト</t>
   </si>
   <si>
-    <t>確認済</t>
+    <t>プロジェクト内で重複しないように採番</t>
   </si>
   <si>
     <t>想定している数まで登録可能か</t>
   </si>
   <si>
+    <t>画面表示</t>
+  </si>
+  <si>
     <t>ユーザー登録画面が表示されている状態</t>
+  </si>
+  <si>
+    <t>期待する画面遷移のケースを作成したか</t>
   </si>
   <si>
     <t>1. 登録画面に有効なデータを入力
@@ -131,10 +191,10 @@
 上記内容をデータベースのデータが100個になるまで繰り返す</t>
   </si>
   <si>
-    <t>入力値検証</t>
-  </si>
-  <si>
-    <t>正常値（代表値）のテストケースを作成したか</t>
+    <t>テスト対象の機能やクラス名</t>
+  </si>
+  <si>
+    <t>ログイン認証、ユーザー登録</t>
   </si>
   <si>
     <t>1. データベースへの登録が成功すること
@@ -142,25 +202,46 @@
 3. データベースに100個のデータが登録されていること</t>
   </si>
   <si>
-    <t>□</t>
-  </si>
-  <si>
-    <t>境界値（最小値・最大値）のテストケースを作成したか</t>
-  </si>
-  <si>
-    <t>8/13 92個目まで登録完了(残り8)</t>
+    <t>要件定義書・設計書と用語を統一</t>
+  </si>
+  <si>
+    <t>エラーメッセージ表示のケースを作成したか</t>
+  </si>
+  <si>
+    <t>何を確認するテストか</t>
+  </si>
+  <si>
+    <t>必須項目のバリデーションケースを作成したか</t>
+  </si>
+  <si>
+    <t>入力値チェック、正常系動作確認</t>
+  </si>
+  <si>
+    <t>100件全て登録でき、データベースにも表示されている</t>
+  </si>
+  <si>
+    <t>合</t>
+  </si>
+  <si>
+    <t>具体的な検証ポイントを明記</t>
+  </si>
+  <si>
+    <t>データ処理</t>
+  </si>
+  <si>
+    <t>データベース登録・更新のケースを作成したか</t>
   </si>
   <si>
     <t>UT-003</t>
   </si>
   <si>
-    <t>空文字・Nullのテストケースを作成したか</t>
-  </si>
-  <si>
     <t>過剰登録したらエラーが出るか</t>
   </si>
   <si>
     <t>ログイン画面が表示されている状態</t>
+  </si>
+  <si>
+    <t>テスト実行前に整える条件</t>
   </si>
   <si>
     <t>1. データベースに100個のデータを登録する
@@ -168,103 +249,19 @@
 3．確認画面に移行し、「登録する」ボタンを押す</t>
   </si>
   <si>
-    <t>不正な形式・特殊文字のテストケースを作成したか</t>
+    <t>データベース削除のケースを作成したか</t>
+  </si>
+  <si>
+    <t>環境設定、データ状態なども記載</t>
   </si>
   <si>
     <t>完了画面に遷移せず、エラーが表示される</t>
   </si>
   <si>
-    <t>機能動作</t>
-  </si>
-  <si>
-    <t>正常系の動作確認ケースを作成したか</t>
-  </si>
-  <si>
-    <t>異常系のエラー処理ケースを作成したか</t>
-  </si>
-  <si>
-    <t>例外処理の確認ケースを作成したか</t>
-  </si>
-  <si>
-    <t>画面表示</t>
-  </si>
-  <si>
-    <t>期待する画面遷移のケースを作成したか</t>
-  </si>
-  <si>
-    <t>エラーメッセージ表示のケースを作成したか</t>
-  </si>
-  <si>
-    <t>必須項目のバリデーションケースを作成したか</t>
-  </si>
-  <si>
-    <t>データ処理</t>
-  </si>
-  <si>
-    <t>データベース登録・更新のケースを作成したか</t>
-  </si>
-  <si>
-    <t>データベース削除のケースを作成したか</t>
+    <t>登録完了画面に遷移し、101件目のデータが登録された</t>
   </si>
   <si>
     <t>データ検索・取得のケースを作成したか</t>
-  </si>
-  <si>
-    <t>権限・認証</t>
-  </si>
-  <si>
-    <t>権限チェックのケースを作成したか</t>
-  </si>
-  <si>
-    <t>ログイン状態の確認ケースを作成したか</t>
-  </si>
-  <si>
-    <t>単体テスト仕様書テンプレート 使い方ガイド</t>
-  </si>
-  <si>
-    <t>項目名</t>
-  </si>
-  <si>
-    <t>説明</t>
-  </si>
-  <si>
-    <t>記載例</t>
-  </si>
-  <si>
-    <t>注意点</t>
-  </si>
-  <si>
-    <t>各テストケースを一意に識別するID</t>
-  </si>
-  <si>
-    <t>UT-001, UT-002</t>
-  </si>
-  <si>
-    <t>プロジェクト内で重複しないように採番</t>
-  </si>
-  <si>
-    <t>テスト対象の機能やクラス名</t>
-  </si>
-  <si>
-    <t>ログイン認証、ユーザー登録</t>
-  </si>
-  <si>
-    <t>要件定義書・設計書と用語を統一</t>
-  </si>
-  <si>
-    <t>何を確認するテストか</t>
-  </si>
-  <si>
-    <t>入力値チェック、正常系動作確認</t>
-  </si>
-  <si>
-    <t>具体的な検証ポイントを明記</t>
-  </si>
-  <si>
-    <t>テスト実行前に整える条件</t>
-  </si>
-  <si>
-    <t>環境設定、データ状態なども記載</t>
   </si>
   <si>
     <t>具体的な実行ステップ</t>
@@ -277,6 +274,12 @@
     <t>番号付きで誰でも実行できるよう詳細に</t>
   </si>
   <si>
+    <t>権限・認証</t>
+  </si>
+  <si>
+    <t>権限チェックのケースを作成したか</t>
+  </si>
+  <si>
     <t>テストデータ</t>
   </si>
   <si>
@@ -287,6 +290,9 @@
   </si>
   <si>
     <t>正常値、境界値、異常値を網羅</t>
+  </si>
+  <si>
+    <t>ログイン状態の確認ケースを作成したか</t>
   </si>
   <si>
     <t>成功時に得られるべき出力</t>
@@ -386,16 +392,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <b/>
       <sz val="14.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font/>
     <font>
@@ -484,35 +490,38 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
@@ -762,148 +771,160 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="A2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="4">
+      <c r="C2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="8">
         <v>46208.0</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>25</v>
+      <c r="J2" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
+      <c r="G3" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="11">
+        <v>46254.0</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="M3" s="3"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
+      <c r="A4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="11">
+        <v>46254.0</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="M4" s="3"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -1909,197 +1930,197 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="2"/>
+      <c r="A2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="3"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="2"/>
+      <c r="A3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="3"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="2"/>
+      <c r="A4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="3"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="2"/>
+      <c r="A5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="3"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="2"/>
+      <c r="A6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="3"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="2"/>
+      <c r="A7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="3"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="2"/>
+      <c r="A8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="3"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="A9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="2"/>
+      <c r="C9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="3"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="2"/>
+      <c r="A10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="3"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="2"/>
+      <c r="A11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="3"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="2"/>
+      <c r="A12" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="3"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="2"/>
+      <c r="A13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="3"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="2"/>
+      <c r="A14" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="3"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="2"/>
+      <c r="A15" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="3"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="2"/>
+      <c r="A16" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="3"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -3104,252 +3125,252 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="9"/>
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>65</v>
+      <c r="A3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>68</v>
+      <c r="B4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>71</v>
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>74</v>
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>76</v>
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="A8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>83</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="A10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>86</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="A11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>89</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="A12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>92</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="A13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>92</v>
+      <c r="A14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>92</v>
+      <c r="A15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="A16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>101</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="s">
-        <v>102</v>
+      <c r="A18" s="12" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>104</v>
+      <c r="A19" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="B20" s="13" t="s">
+      <c r="A20" s="13" t="s">
         <v>105</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>106</v>
+      <c r="A21" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>107</v>
+      <c r="A22" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>108</v>
+      <c r="A23" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1"/>
